--- a/MainTop/21.05.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/21.05.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\21.05.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\21.05.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0549C0CC-737A-4D1A-821F-31079FC77F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7E0FE5-1E1C-4C1B-AC9C-CBB08DB58757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -834,7 +845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -845,6 +856,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1147,11 +1159,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R220"/>
+  <dimension ref="A1:R221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.85546875" customWidth="1"/>
-    <col min="17" max="17" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="3.85546875" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="5" width="4.140625" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="8" width="4.42578125" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" customWidth="1"/>
+    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="11" max="11" width="4.42578125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="4.140625" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" customWidth="1"/>
     <col min="18" max="18" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13475,7 +13500,70 @@
         <v>1</v>
       </c>
     </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B221" s="8">
+        <f>SUM(B2:B220)</f>
+        <v>177</v>
+      </c>
+      <c r="C221" s="8">
+        <f t="shared" ref="C221:P221" si="0">SUM(C2:C220)</f>
+        <v>105</v>
+      </c>
+      <c r="D221" s="8">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="E221" s="8">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="F221" s="8">
+        <f t="shared" si="0"/>
+        <v>159</v>
+      </c>
+      <c r="G221" s="8">
+        <f t="shared" si="0"/>
+        <v>197</v>
+      </c>
+      <c r="H221" s="8">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="I221" s="8">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="J221" s="8">
+        <f t="shared" si="0"/>
+        <v>293</v>
+      </c>
+      <c r="K221" s="8">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="L221" s="8">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="M221" s="8">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="N221" s="8">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="O221" s="8">
+        <f t="shared" si="0"/>
+        <v>1802</v>
+      </c>
+      <c r="P221" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>